--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5743801652892562</v>
+        <v>0.578099173553719</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.001685950413223054</v>
+        <v>0.00540495867768584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 28件／前倒し 11件／期限超過（1か月） 5件／遅れ 4件／期限超過（2か月） 1件</t>
+          <t>おおむね予定どおり 29件／前倒し 11件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="H9" s="30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I9" s="30" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>-13.3</v>
+        <v>-12.4</v>
       </c>
       <c r="K9" s="19" t="n">
         <v>3</v>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
+          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -3620,17 +3620,17 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -3643,9 +3643,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H10" s="30" t="n">
@@ -3658,7 +3658,7 @@
         <v>-12.4</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
@@ -3667,24 +3667,24 @@
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
+          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3694,71 +3694,71 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H11" s="30" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>82.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>-12.4</v>
+        <v>-6.4</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="25" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -3770,13 +3770,13 @@
         <v>30</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -3785,24 +3785,24 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3817,25 +3817,25 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H13" s="30" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -3844,24 +3844,24 @@
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -3910,17 +3910,17 @@
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -4087,17 +4087,17 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -4146,17 +4146,17 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4166,24 +4166,24 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H19" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>0</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -4257,24 +4257,24 @@
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4284,30 +4284,30 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H21" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4500,17 +4500,17 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -4559,17 +4559,17 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -4579,24 +4579,24 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H26" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>0</v>
@@ -4611,39 +4611,39 @@
       </c>
       <c r="M26" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -4729,39 +4729,39 @@
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4800,27 +4800,27 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -4847,24 +4847,24 @@
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -4906,57 +4906,57 @@
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H32" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4977,27 +4977,27 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -5031,44 +5031,44 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H34" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -5095,17 +5095,17 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
@@ -5142,24 +5142,24 @@
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -5169,24 +5169,24 @@
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H36" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>0</v>
@@ -5201,51 +5201,51 @@
       </c>
       <c r="M36" s="18" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H37" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I37" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37" s="30" t="n">
         <v>0</v>
@@ -5260,57 +5260,57 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H38" s="30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
+          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 57.4％　対　予定進捗率 57.3％　乖離 +0.2ポイント</t>
+          <t>加重の実績進捗率 57.8％　対　予定進捗率 57.3％　乖離 +0.5ポイント</t>
         </is>
       </c>
     </row>
@@ -6048,14 +6048,14 @@
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　遅れ 4件</t>
+          <t xml:space="preserve">　遅れ 3件</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 28件</t>
+          <t xml:space="preserve">　おおむね予定どおり 29件</t>
         </is>
       </c>
     </row>
@@ -8600,14 +8600,14 @@
         </is>
       </c>
       <c r="L34" s="21" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M34" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N34" s="18" t="inlineStr">
         <is>
-          <t>**町提出のワークシートによりR5〜R8のサービス別実績を受領。**手帳所持者はR5 539人→R7 508人。うち精神のみ45人→62人（＋37.8％）と増加</t>
+          <t>**町提出のワークシートによりR5〜R8のサービス別実績を受領。****10月15日に、前回計画（令和6年3月）から令和元年〜令和5年の推移を取り出し、素案 第1部第2章2と図 f61 に反映した。**令和元年578人→令和7年508人（▲12.1％）。**身体▲17.7％・療育▲3.9％に対し、精神は＋26.5％と向きが逆。**内訳の和が前回計画の「計」と一致することを自己点検で確かめている。**令和6年のみ手元になく、推計で埋めずに空欄としている**</t>
         </is>
       </c>
       <c r="O34" s="18" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.578099173553719</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.00540495867768584</v>
+        <v>0.009123966942148627</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 29件／前倒し 11件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
+          <t>おおむね予定どおり 30件／前倒し 11件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
@@ -3584,9 +3584,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H9" s="30" t="n">
@@ -3599,7 +3599,7 @@
         <v>-12.4</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" s="25" t="inlineStr">
         <is>
@@ -3608,24 +3608,24 @@
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
+          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3635,71 +3635,71 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H10" s="30" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>82.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>-12.4</v>
+        <v>-6.4</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -3711,13 +3711,13 @@
         <v>30</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
@@ -3726,24 +3726,24 @@
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -3758,25 +3758,25 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H12" s="30" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -3785,24 +3785,24 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -4028,17 +4028,17 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -4087,17 +4087,17 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -4107,24 +4107,24 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H18" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="30" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -4198,24 +4198,24 @@
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4225,30 +4225,30 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4441,17 +4441,17 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -4500,17 +4500,17 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4520,24 +4520,24 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H25" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>0</v>
@@ -4552,39 +4552,39 @@
       </c>
       <c r="M25" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="M26" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -4670,39 +4670,39 @@
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4741,27 +4741,27 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -4788,24 +4788,24 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -4847,57 +4847,57 @@
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H31" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4918,27 +4918,27 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -4972,44 +4972,44 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H33" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="30" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -5036,17 +5036,17 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -5083,24 +5083,24 @@
       </c>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -5110,24 +5110,24 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H35" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>0</v>
@@ -5142,51 +5142,51 @@
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H36" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>0</v>
@@ -5201,57 +5201,57 @@
       </c>
       <c r="M36" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H37" s="30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I37" s="30" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
+          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="H38" s="30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K38" s="19" t="n">
         <v>3</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
+          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 57.8％　対　予定進捗率 57.3％　乖離 +0.5ポイント</t>
+          <t>加重の実績進捗率 58.2％　対　予定進捗率 57.3％　乖離 +0.9ポイント</t>
         </is>
       </c>
     </row>
@@ -6048,14 +6048,14 @@
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　遅れ 3件</t>
+          <t xml:space="preserve">　遅れ 2件</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 29件</t>
+          <t xml:space="preserve">　おおむね予定どおり 30件</t>
         </is>
       </c>
     </row>
@@ -8527,14 +8527,14 @@
         </is>
       </c>
       <c r="L33" s="21" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M33" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N33" s="18" t="inlineStr">
         <is>
-          <t>**前回計画（128頁）と前回調査報告書（110頁）を令和8年10月7日に受領。**第3部第5章の目標31項目を読み出し、アンケート設問との対応を整理した（2-13）。前回アンケート（280件・22件）の検証も作成済み</t>
+          <t>**前回計画（128頁）と前回調査報告書（110頁）を令和8年10月7日に受領。**第3部第5章の目標31項目を読み出し、アンケート設問との対応を整理した（2-13）。前回アンケート（280件・22件）の検証も作成済み。**10月15日に、前回計画から第6期の実績・第7期の見込量を44サービスぶん読み取り（ono_shogai_zenkai.py）、素案 第1部第3章2に反映した。** 書き写さず原本のPDFを毎回読む形にしている。**前回計画に3件の誤りを見つけた**（短期入所の見込量の置き方／障がい児の人と人日の入れ替わり／単位の誤り2件。いずれも確認事項62・63）</t>
         </is>
       </c>
       <c r="O33" s="18" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261015.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5818181818181818</v>
+        <v>0.5921487603305785</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.009123966942148627</v>
+        <v>0.01945454545454531</v>
       </c>
     </row>
     <row r="8">
@@ -3615,32 +3615,32 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -3652,13 +3652,13 @@
         <v>30</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
@@ -3667,24 +3667,24 @@
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3699,25 +3699,25 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H11" s="30" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>35.5</v>
+        <v>100</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
@@ -3726,24 +3726,24 @@
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -3792,17 +3792,17 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -3969,17 +3969,17 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -4028,17 +4028,17 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4048,24 +4048,24 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H17" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="30" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -4139,24 +4139,24 @@
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4166,30 +4166,30 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H19" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4382,17 +4382,17 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -4441,17 +4441,17 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4461,24 +4461,24 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H24" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>0</v>
@@ -4493,39 +4493,39 @@
       </c>
       <c r="M24" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="M25" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -4611,39 +4611,39 @@
       </c>
       <c r="M26" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4682,27 +4682,27 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -4729,24 +4729,24 @@
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -4788,57 +4788,57 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H30" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4859,27 +4859,27 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -4913,44 +4913,44 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H32" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="30" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -5024,24 +5024,24 @@
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -5051,24 +5051,24 @@
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H34" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>0</v>
@@ -5083,51 +5083,51 @@
       </c>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H35" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>0</v>
@@ -5142,57 +5142,57 @@
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H36" s="30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M36" s="18" t="inlineStr">
         <is>
-          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
+          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
         </is>
       </c>
     </row>
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="H37" s="30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I37" s="30" t="n">
-        <v>73.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K37" s="19" t="n">
         <v>3</v>
@@ -5260,24 +5260,24 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
+          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -5295,19 +5295,19 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="H38" s="30" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>82.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="K38" s="19" t="n">
         <v>3</v>
@@ -5319,54 +5319,54 @@
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
+          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G39" s="25" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H39" s="30" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>46.7</v>
+        <v>36.4</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="K39" s="19" t="n">
         <v>3</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
@@ -5419,16 +5419,16 @@
         </is>
       </c>
       <c r="H40" s="30" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>28.9</v>
+        <v>69.7</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>11.1</v>
+        <v>20.3</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" s="31" t="inlineStr">
         <is>
@@ -5437,24 +5437,24 @@
       </c>
       <c r="M40" s="18" t="inlineStr">
         <is>
-          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="H41" s="30" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>69.7</v>
+        <v>48.9</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="K41" s="19" t="n">
         <v>3</v>
@@ -5496,24 +5496,24 @@
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
@@ -5537,16 +5537,16 @@
         </is>
       </c>
       <c r="H42" s="30" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>48.9</v>
+        <v>15.4</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>21.1</v>
+        <v>24.6</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="31" t="inlineStr">
         <is>
@@ -5555,24 +5555,24 @@
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>回収票の点検・ナンバリング・データ入力</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -5582,30 +5582,30 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H43" s="30" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>15.4</v>
+        <v>73.3</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>24.6</v>
+        <v>26.7</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="31" t="inlineStr">
         <is>
@@ -5614,24 +5614,24 @@
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>回収票の点検・ナンバリング・データ入力</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -5646,25 +5646,25 @@
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H44" s="30" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>73.3</v>
+        <v>28.9</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="31" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 58.2％　対　予定進捗率 57.3％　乖離 +0.9ポイント</t>
+          <t>加重の実績進捗率 59.2％　対　予定進捗率 57.3％　乖離 +1.9ポイント</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="N33" s="18" t="inlineStr">
         <is>
-          <t>**前回計画（128頁）と前回調査報告書（110頁）を令和8年10月7日に受領。**第3部第5章の目標31項目を読み出し、アンケート設問との対応を整理した（2-13）。前回アンケート（280件・22件）の検証も作成済み。**10月15日に、前回計画から第6期の実績・第7期の見込量を44サービスぶん読み取り（ono_shogai_zenkai.py）、素案 第1部第3章2に反映した。** 書き写さず原本のPDFを毎回読む形にしている。**前回計画に3件の誤りを見つけた**（短期入所の見込量の置き方／障がい児の人と人日の入れ替わり／単位の誤り2件。いずれも確認事項62・63）</t>
+          <t>**前回計画（128頁）と前回調査報告書（110頁）を令和8年10月7日に受領。**第3部第5章の目標31項目を読み出し、アンケート設問との対応を整理した（2-13）。前回アンケート（280件・22件）の検証も作成済み。**10月15日に、前回計画から第6期の実績・第7期の見込量を44サービスぶん読み取り（ono_shogai_zenkai.py）、素案 第1部第3章2に反映した。** 書き写さず原本のPDFを毎回読む形にしている。**前回計画に3件の誤りを見つけた**（短期入所の見込量の置き方／障がい児の人と人日の入れ替わり／単位の誤り2件。いずれも確認事項64・65）</t>
         </is>
       </c>
       <c r="O33" s="18" t="inlineStr">
@@ -8966,14 +8966,14 @@
         </is>
       </c>
       <c r="L39" s="21" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M39" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N39" s="18" t="inlineStr">
         <is>
-          <t>**設定シート（24項目）を受領。ただしレッドチームレビューで「精神障害にも対応した地域包括ケアシステム」「人材確保・生産性向上」の2分野が丸ごと欠落していることを検出。**一般就労の4項目は基準値（R6実績）未入力で目標値が算出できていない。施設入所系（R7年度末基準）と一般就労系（R6年度基準）で基準年度が混在</t>
+          <t>**10月15日に前回計画の成果目標を検証し、①（施設入所者の地域生活移行）が成り立たないことを確かめた。**入所者26人に対し移行31人（119.2％）・削減22人（84.6％）で、削減後4人のはずが同じ計画の見込量は15人。国の指針を26人に当てはめると移行2人・削減2人。**ほかの目標は本町の規模に照らして無理がなく、成り立たないのは①だけ**（素案 第3部第1章1-1・確認事項63）。**設定シート（24項目）を受領。ただしレッドチームレビューで「精神障害にも対応した地域包括ケアシステム」「人材確保・生産性向上」の2分野が丸ごと欠落していることを検出。**一般就労の4項目は基準値（R6実績）未入力で目標値が算出できていない。施設入所系（R7年度末基準）と一般就労系（R6年度基準）で基準年度が混在</t>
         </is>
       </c>
       <c r="O39" s="18" t="inlineStr">
@@ -9039,14 +9039,14 @@
         </is>
       </c>
       <c r="L40" s="21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M40" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N40" s="18" t="inlineStr">
         <is>
-          <t>**見込量・目標値設定シート（9シート）を受領し、レッドチームレビューを実施（04_算定・見込量）。算式は利用者数22行・利用量7行の全行で再現一致し、人口・手帳の内訳合計とサマリーの突合も全一致。**一方、重大5件を含む16件の不具合を検出した（成果目標の基準年度の混在、2分野の欠落、セルフプラン0件目標と見込量の不整合、地域生活支援事業21項目中11項目の未設定、居宅介護の異常値処理ほか）</t>
+          <t>**あわせて、地域生活支援事業の4事業（意思疎通支援・手話奉仕員養成・移動支援・地域活動支援センター）が、前回計画で実績も見込量もすべて0であることを確かめた。**令和7年4月に手話言語条例を施行しており、0のままにはできない（素案 第3部第2章2-2・確認事項62〈最優先〉）。**10月15日に、見込量の置き方を「人数×1人あたり日数」に具体化した（素案 第3部第2章2-1・図 f62）。**前回計画の第6期は、量が見込みを下回った原因が人数ではなく1人あたり日数にあった（放課後等デイサービスは見込み11.4日に対し実績3.2日＝29％）。**1人あたり日数は実績の値を出発点とし、引き上げる場合は施策の手当てと対にする。****見込量・目標値設定シート（9シート）を受領し、レッドチームレビューを実施（04_算定・見込量）。算式は利用者数22行・利用量7行の全行で再現一致し、人口・手帳の内訳合計とサマリーの突合も全一致。**一方、重大5件を含む16件の不具合を検出した（成果目標の基準年度の混在、2分野の欠落、セルフプラン0件目標と見込量の不整合、地域生活支援事業21項目中11項目の未設定、居宅介護の異常値処理ほか）</t>
         </is>
       </c>
       <c r="O40" s="18" t="inlineStr">
